--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-pr-studie-ein-auschluss-kriterium.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-pr-studie-ein-auschluss-kriterium.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:57:45+00:00</t>
+    <t>2026-08-31T21:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-pr-studie-ein-auschluss-kriterium.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-pr-studie-ein-auschluss-kriterium.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T21:27:29+00:00</t>
+    <t>2026-08-31T21:32:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-pr-studie-ein-auschluss-kriterium.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-pr-studie-ein-auschluss-kriterium.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T21:32:33+00:00</t>
+    <t>2026-08-31T22:12:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-pr-studie-ein-auschluss-kriterium.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-pr-studie-ein-auschluss-kriterium.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T22:12:11+00:00</t>
+    <t>2026-09-01T10:00:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
